--- a/data/air_permits.xlsx
+++ b/data/air_permits.xlsx
@@ -18,14 +18,16 @@
     <sheet sheetId="9" name="中和區" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="五股區" state="visible" r:id="rId13"/>
     <sheet sheetId="12" name="龜山區" state="visible" r:id="rId14"/>
-    <sheet sheetId="11" name="總表" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="板橋區_下午0218" state="visible" r:id="rId15"/>
+    <sheet sheetId="14" name="板橋區_下午0221" state="visible" r:id="rId16"/>
+    <sheet sheetId="11" name="總表" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12338" uniqueCount="3368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12434" uniqueCount="3370">
   <si>
     <t>county</t>
   </si>
@@ -10399,6 +10401,12 @@
   </si>
   <si>
     <t>龜山區</t>
+  </si>
+  <si>
+    <t>板橋區_下午0218</t>
+  </si>
+  <si>
+    <t>板橋區_下午0221</t>
   </si>
 </sst>
 </file>
@@ -14699,7 +14707,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K644"/>
+  <dimension ref="A1:K648"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -37252,6 +37260,146 @@
       </c>
       <c r="K644" t="s">
         <v>3367</v>
+      </c>
+    </row>
+    <row r="645" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A645" t="s">
+        <v>10</v>
+      </c>
+      <c r="B645" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C645" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D645" t="s">
+        <v>1690</v>
+      </c>
+      <c r="E645">
+        <v>1</v>
+      </c>
+      <c r="F645" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G645" t="s">
+        <v>15</v>
+      </c>
+      <c r="H645" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="I645" t="s">
+        <v>813</v>
+      </c>
+      <c r="J645" t="s">
+        <v>813</v>
+      </c>
+      <c r="K645" t="s">
+        <v>3368</v>
+      </c>
+    </row>
+    <row r="646" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A646" t="s">
+        <v>10</v>
+      </c>
+      <c r="B646" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C646" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D646" t="s">
+        <v>1690</v>
+      </c>
+      <c r="E646">
+        <v>1</v>
+      </c>
+      <c r="F646" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G646" t="s">
+        <v>15</v>
+      </c>
+      <c r="H646" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="I646" t="s">
+        <v>813</v>
+      </c>
+      <c r="J646" t="s">
+        <v>813</v>
+      </c>
+      <c r="K646" t="s">
+        <v>3369</v>
+      </c>
+    </row>
+    <row r="647" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A647" t="s">
+        <v>10</v>
+      </c>
+      <c r="B647" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C647" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D647" t="s">
+        <v>1695</v>
+      </c>
+      <c r="E647">
+        <v>1</v>
+      </c>
+      <c r="F647" s="4" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G647" t="s">
+        <v>15</v>
+      </c>
+      <c r="H647" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="I647" t="s">
+        <v>1697</v>
+      </c>
+      <c r="J647" t="s">
+        <v>1697</v>
+      </c>
+      <c r="K647" t="s">
+        <v>3369</v>
+      </c>
+    </row>
+    <row r="648" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A648" t="s">
+        <v>10</v>
+      </c>
+      <c r="B648" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C648" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D648" t="s">
+        <v>1705</v>
+      </c>
+      <c r="E648">
+        <v>1</v>
+      </c>
+      <c r="F648" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G648" t="s">
+        <v>15</v>
+      </c>
+      <c r="H648" s="4" t="s">
+        <v>1706</v>
+      </c>
+      <c r="I648" t="s">
+        <v>1707</v>
+      </c>
+      <c r="J648" t="s">
+        <v>1707</v>
+      </c>
+      <c r="K648" t="s">
+        <v>3369</v>
       </c>
     </row>
   </sheetData>
@@ -42238,6 +42386,242 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="35" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="10" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="I2" t="s">
+        <v>813</v>
+      </c>
+      <c r="J2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="35" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="10" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="I2" t="s">
+        <v>813</v>
+      </c>
+      <c r="J2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1695</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1697</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1705</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>1706</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1707</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
